--- a/artfynd/A 32394-2026 artfynd.xlsx
+++ b/artfynd/A 32394-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136009461</v>
       </c>
       <c r="B2" t="n">
-        <v>92264</v>
+        <v>92278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136009577</v>
       </c>
       <c r="B3" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136009542</v>
       </c>
       <c r="B4" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32394-2026 artfynd.xlsx
+++ b/artfynd/A 32394-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136009461</v>
       </c>
       <c r="B2" t="n">
-        <v>92278</v>
+        <v>92279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136009577</v>
       </c>
       <c r="B3" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32394-2026 artfynd.xlsx
+++ b/artfynd/A 32394-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136009461</v>
       </c>
       <c r="B2" t="n">
-        <v>92279</v>
+        <v>92280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136009577</v>
       </c>
       <c r="B3" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32394-2026 artfynd.xlsx
+++ b/artfynd/A 32394-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136009461</v>
       </c>
       <c r="B2" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136009577</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136009542</v>
       </c>
       <c r="B4" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32394-2026 artfynd.xlsx
+++ b/artfynd/A 32394-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136009461</v>
       </c>
       <c r="B2" t="n">
-        <v>92281</v>
+        <v>92287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136009577</v>
       </c>
       <c r="B3" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136009542</v>
       </c>
       <c r="B4" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32394-2026 artfynd.xlsx
+++ b/artfynd/A 32394-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136009461</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>92288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136009577</v>
       </c>
       <c r="B3" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136009542</v>
       </c>
       <c r="B4" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
